--- a/marketing_report/outputs/Cursos/Reporte_Asesores/17_reporte_asesores.xlsx
+++ b/marketing_report/outputs/Cursos/Reporte_Asesores/17_reporte_asesores.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,6 +443,106 @@
         <is>
           <t>Total_Inscriptos</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Contact Center</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sin Asignar</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Camila Gisela Pacheco</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Carolina Eugenia Ferrer</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Francisco Gerardo Jover</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gimena Vallejos</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Jorge Ariel Cabaña</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Rocío Belén Leiva</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UCASAL Prod</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VIRGINIA MARIA HUERGO CORNEJO</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -488,7 +588,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -503,7 +603,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -518,7 +618,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -1086,10 +1186,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>40.90909090909091</v>
+        <v>36.58536585365854</v>
       </c>
     </row>
     <row r="3">
@@ -1099,10 +1199,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>29.54545454545455</v>
+        <v>29.26829268292683</v>
       </c>
     </row>
     <row r="4">
@@ -1112,10 +1212,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>18.18181818181818</v>
+        <v>21.95121951219512</v>
       </c>
     </row>
     <row r="5">
@@ -1128,7 +1228,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>11.36363636363636</v>
+        <v>12.19512195121951</v>
       </c>
     </row>
   </sheetData>
